--- a/StructureDefinition-vital-sign-observation-profile.xlsx
+++ b/StructureDefinition-vital-sign-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-vital-sign-observation-profile.xlsx
+++ b/StructureDefinition-vital-sign-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="545">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1342,6 +1342,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -7391,7 +7395,7 @@
         <v>416</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7406,7 +7410,7 @@
         <v>407</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>20</v>
@@ -7414,10 +7418,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7443,10 +7447,10 @@
         <v>413</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7497,7 +7501,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7509,7 +7513,7 @@
         <v>416</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7524,7 +7528,7 @@
         <v>407</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>20</v>
@@ -7532,10 +7536,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7561,10 +7565,10 @@
         <v>234</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7594,10 +7598,10 @@
         <v>332</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7615,7 +7619,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7642,7 +7646,7 @@
         <v>407</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>20</v>
@@ -7650,10 +7654,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7679,16 +7683,16 @@
         <v>234</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7716,10 +7720,10 @@
         <v>240</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7737,7 +7741,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7758,10 +7762,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>347</v>
@@ -7772,10 +7776,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7801,16 +7805,16 @@
         <v>234</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7838,10 +7842,10 @@
         <v>252</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7859,7 +7863,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7880,10 +7884,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>347</v>
@@ -7894,10 +7898,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7920,17 +7924,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7979,7 +7983,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8006,7 +8010,7 @@
         <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -8014,10 +8018,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8040,13 +8044,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8097,7 +8101,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8124,7 +8128,7 @@
         <v>407</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -8132,10 +8136,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8158,16 +8162,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8217,7 +8221,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8241,7 +8245,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>200</v>
@@ -8252,10 +8256,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8278,16 +8282,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8337,7 +8341,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8361,10 +8365,10 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>20</v>
@@ -8372,10 +8376,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8401,16 +8405,16 @@
         <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8459,7 +8463,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8483,10 +8487,10 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>20</v>
@@ -8494,10 +8498,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8612,10 +8616,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8732,10 +8736,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8854,10 +8858,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8883,13 +8887,13 @@
         <v>234</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>250</v>
@@ -8921,7 +8925,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8939,7 +8943,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -8960,7 +8964,7 @@
         <v>257</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>259</v>
@@ -8974,10 +8978,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9000,16 +9004,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>319</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>321</v>
@@ -9061,7 +9065,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9082,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>324</v>
@@ -9096,10 +9100,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9214,10 +9218,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9287,16 +9291,16 @@
         <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>190</v>
@@ -9334,10 +9338,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9360,19 +9364,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9421,7 +9425,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9445,10 +9449,10 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>20</v>
@@ -9456,10 +9460,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9485,20 +9489,20 @@
         <v>113</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="R62" t="s" s="2">
         <v>20</v>
@@ -9522,10 +9526,10 @@
         <v>117</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9543,7 +9547,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9567,10 +9571,10 @@
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>20</v>
@@ -9578,10 +9582,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9607,14 +9611,14 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9624,7 +9628,7 @@
         <v>20</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>20</v>
@@ -9663,7 +9667,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9687,10 +9691,10 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>20</v>
@@ -9698,10 +9702,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9727,14 +9731,14 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9744,7 +9748,7 @@
         <v>20</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>20</v>
@@ -9783,7 +9787,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9792,7 +9796,7 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -9807,10 +9811,10 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>20</v>
@@ -9818,10 +9822,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9847,16 +9851,16 @@
         <v>113</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9866,7 +9870,7 @@
         <v>20</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>20</v>
@@ -9905,7 +9909,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9914,7 +9918,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -9929,10 +9933,10 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>20</v>
@@ -9940,10 +9944,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9969,13 +9973,13 @@
         <v>234</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>331</v>
@@ -10027,7 +10031,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10062,10 +10066,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10149,7 +10153,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10184,10 +10188,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10213,10 +10217,10 @@
         <v>82</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>404</v>
@@ -10271,7 +10275,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-vital-sign-observation-profile.xlsx
+++ b/StructureDefinition-vital-sign-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
